--- a/data/reference/dictionaries_nlp/resultados_clasificacion_temas/pmi_confianza_corpus_unido_consolidado_normalizado.xlsx
+++ b/data/reference/dictionaries_nlp/resultados_clasificacion_temas/pmi_confianza_corpus_unido_consolidado_normalizado.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -681,7 +681,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24_40</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -778,7 +778,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24_41</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -875,7 +875,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24_42</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -972,7 +972,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24_43</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1069,7 +1069,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24_44</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1166,7 +1166,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24_45</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1263,7 +1263,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24_46</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1360,7 +1360,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>24_47</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1457,7 +1457,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24_48</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1554,7 +1554,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24_49</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1651,7 +1651,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>24_50</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1748,7 +1748,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24_51</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1845,7 +1845,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24_52</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1942,7 +1942,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25_01</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -2039,7 +2039,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25_02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -2136,7 +2136,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25_03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -2233,7 +2233,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25_04</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -2330,7 +2330,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25_05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -2427,7 +2427,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25_06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -2524,7 +2524,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25_07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -2621,7 +2621,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25_08</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -2718,7 +2718,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25_09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -2815,7 +2815,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25_10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -2912,7 +2912,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25_11</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -3009,7 +3009,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25_12</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -3106,7 +3106,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>25_13</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -3203,7 +3203,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25_14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -3300,7 +3300,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25_15</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -3397,7 +3397,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25_16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -3494,7 +3494,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25_17</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -3591,7 +3591,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25_18</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -3688,7 +3688,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25_19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -3785,7 +3785,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25_20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
@@ -3882,7 +3882,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25_21</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -3979,7 +3979,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25_22</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
@@ -4076,7 +4076,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25_23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
@@ -4173,7 +4173,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>25_24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -4270,7 +4270,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>25_25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -4367,7 +4367,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>25_26</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -4464,7 +4464,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25_27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
@@ -4561,7 +4561,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25_28</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
@@ -4658,7 +4658,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25_29</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -4755,7 +4755,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25_30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -4852,7 +4852,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25_31</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -4949,7 +4949,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>25_32</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -5046,7 +5046,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>25_33</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -5143,7 +5143,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>25_34</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
@@ -5240,7 +5240,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>25_35</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -5337,7 +5337,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25_36</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
@@ -5434,7 +5434,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25_37</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -5531,7 +5531,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>25_38</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -5628,7 +5628,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>25_39</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -5725,7 +5725,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25_40</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -5822,7 +5822,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25_41</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -5919,7 +5919,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>25_42</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -6016,7 +6016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>25_43</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
@@ -6113,7 +6113,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>25_44</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
@@ -6210,7 +6210,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>25_45</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
@@ -6307,7 +6307,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>25_46</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
@@ -6404,7 +6404,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>25_47</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
@@ -6501,7 +6501,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>25_48</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
@@ -6598,7 +6598,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>25_49</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
@@ -6695,7 +6695,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25_50</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
@@ -6792,7 +6792,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>25_51</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
@@ -6889,7 +6889,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25_52</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
@@ -6986,7 +6986,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>26_01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
@@ -7083,7 +7083,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>26_02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
@@ -7180,7 +7180,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>26_03</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
@@ -7277,7 +7277,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>26_04</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
@@ -7374,7 +7374,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>26_05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
@@ -7471,7 +7471,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>26_06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
@@ -7568,7 +7568,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>26_07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
@@ -7665,7 +7665,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>26_08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -7762,7 +7762,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>26_09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
@@ -7859,7 +7859,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26_10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -7954,129 +7954,905 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>-1.5346</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-1.2892</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>-0.3516</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>5.1237</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>-0.1761</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>5.1184</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>-1.9431</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>-4.172</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>-4.0996</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>1.8234</v>
+      </c>
+      <c r="R77" s="4" t="n">
+        <v>-4.3034</v>
+      </c>
+      <c r="S77" s="4" t="n">
+        <v>-4.1048</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>4.0212</v>
+      </c>
+      <c r="U77" s="4" t="n">
+        <v>-2.7523</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>3.3922</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>3.8642</v>
+      </c>
+      <c r="X77" s="4" t="n">
+        <v>-1.3758</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>3.6968</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2.2819</v>
+      </c>
+      <c r="AA77" s="4" t="n">
+        <v>-1.6165</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>1.4839</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="AD77" s="4" t="n">
+        <v>-4.0636</v>
+      </c>
+      <c r="AE77" s="4" t="n">
+        <v>-4.0035</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>-2.7467</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>-2.7071</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1.4729</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>-0.4656</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1.2599</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>4.4786</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>4.4773</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>-1.8612</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>-1.8296</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>-3.6312</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>-3.5412</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>1.6473</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>-3.4769</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>-3.1702</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>3.4595</v>
+      </c>
+      <c r="U78" s="4" t="n">
+        <v>-2.1054</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.9444</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>5.7787</v>
+      </c>
+      <c r="X78" s="4" t="n">
+        <v>-0.8456</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>5.7576</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>3.4617</v>
+      </c>
+      <c r="AA78" s="4" t="n">
+        <v>-2.3829</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>2.7659</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="AD78" s="4" t="n">
+        <v>-2.6556</v>
+      </c>
+      <c r="AE78" s="4" t="n">
+        <v>-2.5873</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>-2.6028</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-2.3645</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1.7853</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>-1.0946</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1.2088</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>-3.0794</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>-3.0567</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>-4.0889</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>-4.0336</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>1.8421</v>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>-3.9955</v>
+      </c>
+      <c r="S79" s="4" t="n">
+        <v>-3.7403</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="U79" s="4" t="n">
+        <v>-2.7722</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>-1.5526</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>4.3873</v>
+      </c>
+      <c r="X79" s="4" t="n">
+        <v>-1.3651</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>4.2743</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>3.1379</v>
+      </c>
+      <c r="AA79" s="4" t="n">
+        <v>-2.122</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>2.4462</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="AD79" s="4" t="n">
+        <v>-3.3832</v>
+      </c>
+      <c r="AE79" s="4" t="n">
+        <v>-3.2575</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>-1.1166</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-1.0856</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>-0.673</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>-1.4711</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>-1.3855</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>1.4385</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>-3.6612</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>-3.4517</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>1.5104</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>-3.5504</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>-3.3027</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>2.0997</v>
+      </c>
+      <c r="U80" s="4" t="n">
+        <v>-1.8477</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>3.6005</v>
+      </c>
+      <c r="X80" s="4" t="n">
+        <v>-1.1864</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>3.4402</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>3.0526</v>
+      </c>
+      <c r="AA80" s="4" t="n">
+        <v>-1.6657</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>2.6146</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AD80" s="4" t="n">
+        <v>-3.4428</v>
+      </c>
+      <c r="AE80" s="4" t="n">
+        <v>-3.4088</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>-2.9573</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-2.905</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2.6321</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>-0.7219</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2.4725</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>-2.5166</v>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>-2.5102</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>1.3749</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>-3.1085</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>-2.8138</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>1.1887</v>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>-3.0673</v>
+      </c>
+      <c r="S81" s="4" t="n">
+        <v>-2.8283</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>2.1344</v>
+      </c>
+      <c r="U81" s="4" t="n">
+        <v>-2.274</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>-0.5322</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>4.7339</v>
+      </c>
+      <c r="X81" s="4" t="n">
+        <v>-1.3501</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>4.6474</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2.7632</v>
+      </c>
+      <c r="AA81" s="4" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>1.8978</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>1.8877</v>
+      </c>
+      <c r="AD81" s="4" t="n">
+        <v>-3.3528</v>
+      </c>
+      <c r="AE81" s="4" t="n">
+        <v>-2.9099</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>-1.643</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>-1.5789</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1.0221</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>-0.5624</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>-2.0426</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>-1.9685</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>-4.1604</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>-4.0853</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>-3.9013</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>-2.769</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.6725</v>
+      </c>
+      <c r="U82" s="4" t="n">
+        <v>-3.173</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>-1.8654</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>4.3789</v>
+      </c>
+      <c r="X82" s="4" t="n">
+        <v>-1.4892</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>4.2478</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>1.6866</v>
+      </c>
+      <c r="AA82" s="4" t="n">
+        <v>-2.2104</v>
+      </c>
+      <c r="AB82" s="4" t="n">
+        <v>-1.2685</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>0.5974</v>
+      </c>
+      <c r="AD82" s="4" t="n">
+        <v>-2.9463</v>
+      </c>
+      <c r="AE82" s="4" t="n">
+        <v>-2.8469</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>-2.2735</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>-2.1914</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>-0.5065</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.7788</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>3.6985</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>-0.0638</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>3.6934</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>-1.559</v>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>-1.5138</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>-4.2835</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>-4.2366</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>1.5467</v>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>-4.1642</v>
+      </c>
+      <c r="S83" s="4" t="n">
+        <v>-4.0006</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.8576</v>
+      </c>
+      <c r="U83" s="4" t="n">
+        <v>-3.3365</v>
+      </c>
+      <c r="V83" s="4" t="n">
+        <v>-1.9461</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>3.8601</v>
+      </c>
+      <c r="X83" s="4" t="n">
+        <v>-1.6214</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>3.6375</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>1.3895</v>
+      </c>
+      <c r="AA83" s="4" t="n">
+        <v>-1.6831</v>
+      </c>
+      <c r="AB83" s="4" t="n">
+        <v>-0.6701</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="AD83" s="4" t="n">
+        <v>-3.1317</v>
+      </c>
+      <c r="AE83" s="4" t="n">
+        <v>-3.0611</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>-1.2732</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>-1.2498</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1.9865</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>-0.369</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>1.8763</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>3.0365</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>-0.2399</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>3.0043</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>-2.0539</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>-2.0407</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>-4.0548</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>-3.9503</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>1.6203</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>-3.8672</v>
+      </c>
+      <c r="S84" s="4" t="n">
+        <v>-3.646</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.6413</v>
+      </c>
+      <c r="U84" s="4" t="n">
+        <v>-3.7155</v>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>-2.9814</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>3.7522</v>
+      </c>
+      <c r="X84" s="4" t="n">
+        <v>-1.6236</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>3.5101</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="AA84" s="4" t="n">
+        <v>-1.6614</v>
+      </c>
+      <c r="AB84" s="4" t="n">
+        <v>-0.506</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AD84" s="4" t="n">
+        <v>-2.6749</v>
+      </c>
+      <c r="AE84" s="4" t="n">
+        <v>-2.636</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(B2:B76)</f>
+      <c r="B85" s="7">
+        <f>SUM(B2:B84)</f>
         <v/>
       </c>
-      <c r="C77" s="7">
-        <f>SUM(C2:C76)</f>
+      <c r="C85" s="7">
+        <f>SUM(C2:C84)</f>
         <v/>
       </c>
-      <c r="D77" s="7">
-        <f>SUM(D2:D76)</f>
+      <c r="D85" s="7">
+        <f>SUM(D2:D84)</f>
         <v/>
       </c>
-      <c r="E77" s="7">
-        <f>SUM(E2:E76)</f>
+      <c r="E85" s="7">
+        <f>SUM(E2:E84)</f>
         <v/>
       </c>
-      <c r="F77" s="7">
-        <f>SUM(F2:F76)</f>
+      <c r="F85" s="7">
+        <f>SUM(F2:F84)</f>
         <v/>
       </c>
-      <c r="G77" s="7">
-        <f>SUM(G2:G76)</f>
+      <c r="G85" s="7">
+        <f>SUM(G2:G84)</f>
         <v/>
       </c>
-      <c r="H77" s="7">
-        <f>SUM(H2:H76)</f>
+      <c r="H85" s="7">
+        <f>SUM(H2:H84)</f>
         <v/>
       </c>
-      <c r="I77" s="7">
-        <f>SUM(I2:I76)</f>
+      <c r="I85" s="7">
+        <f>SUM(I2:I84)</f>
         <v/>
       </c>
-      <c r="J77" s="7">
-        <f>SUM(J2:J76)</f>
+      <c r="J85" s="7">
+        <f>SUM(J2:J84)</f>
         <v/>
       </c>
-      <c r="K77" s="7">
-        <f>SUM(K2:K76)</f>
+      <c r="K85" s="7">
+        <f>SUM(K2:K84)</f>
         <v/>
       </c>
-      <c r="L77" s="7">
-        <f>SUM(L2:L76)</f>
+      <c r="L85" s="7">
+        <f>SUM(L2:L84)</f>
         <v/>
       </c>
-      <c r="M77" s="7">
-        <f>SUM(M2:M76)</f>
+      <c r="M85" s="7">
+        <f>SUM(M2:M84)</f>
         <v/>
       </c>
-      <c r="N77" s="7">
-        <f>SUM(N2:N76)</f>
+      <c r="N85" s="7">
+        <f>SUM(N2:N84)</f>
         <v/>
       </c>
-      <c r="O77" s="7">
-        <f>SUM(O2:O76)</f>
+      <c r="O85" s="7">
+        <f>SUM(O2:O84)</f>
         <v/>
       </c>
-      <c r="P77" s="7">
-        <f>SUM(P2:P76)</f>
+      <c r="P85" s="7">
+        <f>SUM(P2:P84)</f>
         <v/>
       </c>
-      <c r="Q77" s="7">
-        <f>SUM(Q2:Q76)</f>
+      <c r="Q85" s="7">
+        <f>SUM(Q2:Q84)</f>
         <v/>
       </c>
-      <c r="R77" s="7">
-        <f>SUM(R2:R76)</f>
+      <c r="R85" s="7">
+        <f>SUM(R2:R84)</f>
         <v/>
       </c>
-      <c r="S77" s="7">
-        <f>SUM(S2:S76)</f>
+      <c r="S85" s="7">
+        <f>SUM(S2:S84)</f>
         <v/>
       </c>
-      <c r="T77" s="7">
-        <f>SUM(T2:T76)</f>
+      <c r="T85" s="7">
+        <f>SUM(T2:T84)</f>
         <v/>
       </c>
-      <c r="U77" s="7">
-        <f>SUM(U2:U76)</f>
+      <c r="U85" s="7">
+        <f>SUM(U2:U84)</f>
         <v/>
       </c>
-      <c r="V77" s="7">
-        <f>SUM(V2:V76)</f>
+      <c r="V85" s="7">
+        <f>SUM(V2:V84)</f>
         <v/>
       </c>
-      <c r="W77" s="7">
-        <f>SUM(W2:W76)</f>
+      <c r="W85" s="7">
+        <f>SUM(W2:W84)</f>
         <v/>
       </c>
-      <c r="X77" s="7">
-        <f>SUM(X2:X76)</f>
+      <c r="X85" s="7">
+        <f>SUM(X2:X84)</f>
         <v/>
       </c>
-      <c r="Y77" s="7">
-        <f>SUM(Y2:Y76)</f>
+      <c r="Y85" s="7">
+        <f>SUM(Y2:Y84)</f>
         <v/>
       </c>
-      <c r="Z77" s="7">
-        <f>SUM(Z2:Z76)</f>
+      <c r="Z85" s="7">
+        <f>SUM(Z2:Z84)</f>
         <v/>
       </c>
-      <c r="AA77" s="7">
-        <f>SUM(AA2:AA76)</f>
+      <c r="AA85" s="7">
+        <f>SUM(AA2:AA84)</f>
         <v/>
       </c>
-      <c r="AB77" s="7">
-        <f>SUM(AB2:AB76)</f>
+      <c r="AB85" s="7">
+        <f>SUM(AB2:AB84)</f>
         <v/>
       </c>
-      <c r="AC77" s="7">
-        <f>SUM(AC2:AC76)</f>
+      <c r="AC85" s="7">
+        <f>SUM(AC2:AC84)</f>
         <v/>
       </c>
-      <c r="AD77" s="7">
-        <f>SUM(AD2:AD76)</f>
+      <c r="AD85" s="7">
+        <f>SUM(AD2:AD84)</f>
         <v/>
       </c>
-      <c r="AE77" s="7">
-        <f>SUM(AE2:AE76)</f>
+      <c r="AE85" s="7">
+        <f>SUM(AE2:AE84)</f>
         <v/>
       </c>
     </row>
@@ -8091,7 +8867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8317,7 +9093,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24_40</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -8414,7 +9190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24_41</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -8511,7 +9287,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24_42</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -8608,7 +9384,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24_43</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -8705,7 +9481,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24_44</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -8802,7 +9578,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24_45</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -8899,7 +9675,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24_46</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -8996,7 +9772,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>24_47</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -9093,7 +9869,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24_48</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -9190,7 +9966,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24_49</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -9287,7 +10063,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>24_50</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -9384,7 +10160,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24_51</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -9481,7 +10257,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24_52</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -9578,7 +10354,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25_01</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -9675,7 +10451,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25_02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -9772,7 +10548,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25_03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -9869,7 +10645,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25_04</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -9966,7 +10742,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25_05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -10063,7 +10839,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25_06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -10160,7 +10936,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25_07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -10257,7 +11033,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25_08</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -10354,7 +11130,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25_09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -10451,7 +11227,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25_10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -10548,7 +11324,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25_11</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -10645,7 +11421,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25_12</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -10742,7 +11518,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>25_13</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -10839,7 +11615,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25_14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -10936,7 +11712,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25_15</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -11033,7 +11809,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25_16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -11130,7 +11906,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25_17</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -11227,7 +12003,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25_18</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -11324,7 +12100,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25_19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -11421,7 +12197,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25_20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
@@ -11518,7 +12294,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25_21</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -11615,7 +12391,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25_22</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
@@ -11712,7 +12488,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25_23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
@@ -11809,7 +12585,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>25_24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -11906,7 +12682,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>25_25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -12003,7 +12779,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>25_26</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -12100,7 +12876,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25_27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
@@ -12197,7 +12973,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25_28</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
@@ -12294,7 +13070,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25_29</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -12391,7 +13167,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25_30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -12488,7 +13264,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25_31</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -12585,7 +13361,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>25_32</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -12682,7 +13458,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>25_33</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -12779,7 +13555,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>25_34</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
@@ -12876,7 +13652,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>25_35</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -12973,7 +13749,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25_36</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
@@ -13070,7 +13846,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25_37</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -13167,7 +13943,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>25_38</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -13264,7 +14040,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>25_39</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -13361,7 +14137,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25_40</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -13458,7 +14234,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25_41</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -13555,7 +14331,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>25_42</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -13652,7 +14428,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>25_43</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
@@ -13749,7 +14525,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>25_44</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
@@ -13846,7 +14622,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>25_45</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
@@ -13943,7 +14719,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>25_46</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
@@ -14040,7 +14816,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>25_47</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
@@ -14137,7 +14913,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>25_48</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
@@ -14234,7 +15010,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>25_49</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
@@ -14331,7 +15107,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25_50</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
@@ -14428,7 +15204,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>25_51</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
@@ -14525,7 +15301,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25_52</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
@@ -14622,7 +15398,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>26_01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
@@ -14719,7 +15495,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>26_02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
@@ -14816,7 +15592,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>26_03</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
@@ -14913,7 +15689,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>26_04</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
@@ -15010,7 +15786,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>26_05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
@@ -15107,7 +15883,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>26_06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
@@ -15204,7 +15980,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>26_07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
@@ -15301,7 +16077,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>26_08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -15398,7 +16174,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>26_09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
@@ -15495,7 +16271,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26_10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -15590,129 +16366,905 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>-1.2187</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-1.059</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>-0.2421</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>4.9474</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>-0.1245</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>4.9431</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>-1.6287</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>-1.6068</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0.6823</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>-3.6977</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>-3.6288</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="R77" s="4" t="n">
+        <v>-3.9186</v>
+      </c>
+      <c r="S77" s="4" t="n">
+        <v>-3.797</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>3.4587</v>
+      </c>
+      <c r="U77" s="4" t="n">
+        <v>-2.368</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2.7723</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>3.5673</v>
+      </c>
+      <c r="X77" s="4" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>1.4292</v>
+      </c>
+      <c r="AA77" s="4" t="n">
+        <v>-1.5561</v>
+      </c>
+      <c r="AB77" s="4" t="n">
+        <v>-0.319</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="AD77" s="4" t="n">
+        <v>-3.504</v>
+      </c>
+      <c r="AE77" s="4" t="n">
+        <v>-3.459</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>-2.2037</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>-2.1695</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1.2319</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>-0.3652</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>4.2603</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>4.2595</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>-1.5255</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>-1.4806</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>-3.2505</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>-3.1854</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>-3.0737</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>-2.8276</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>2.9284</v>
+      </c>
+      <c r="U78" s="4" t="n">
+        <v>-1.8726</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.3077</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>5.3765</v>
+      </c>
+      <c r="X78" s="4" t="n">
+        <v>-0.6819</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>5.3554</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2.568</v>
+      </c>
+      <c r="AA78" s="4" t="n">
+        <v>-2.0174</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>1.5268</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="AD78" s="4" t="n">
+        <v>-2.1385</v>
+      </c>
+      <c r="AE78" s="4" t="n">
+        <v>-2.0837</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>-2.1471</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-1.9887</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1.5722</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>-0.9373</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>-2.6109</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>-2.5842</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>-3.6053</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>-3.5507</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>1.2956</v>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>-3.597</v>
+      </c>
+      <c r="S79" s="4" t="n">
+        <v>-3.4122</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>1.6639</v>
+      </c>
+      <c r="U79" s="4" t="n">
+        <v>-2.4506</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>-1.7214</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>4.0783</v>
+      </c>
+      <c r="X79" s="4" t="n">
+        <v>-1.0841</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>3.9793</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2.2388</v>
+      </c>
+      <c r="AA79" s="4" t="n">
+        <v>-1.9702</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AD79" s="4" t="n">
+        <v>-2.9943</v>
+      </c>
+      <c r="AE79" s="4" t="n">
+        <v>-2.9052</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>-0.7923</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-0.755</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>-0.1965</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>-1.2722</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>-1.1729</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>-3.3314</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>-3.1612</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>1.0759</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>-3.2138</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>-3.0303</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="U80" s="4" t="n">
+        <v>-1.6219</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>-0.8354</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>3.2917</v>
+      </c>
+      <c r="X80" s="4" t="n">
+        <v>-0.9075</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>3.1565</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2.2194</v>
+      </c>
+      <c r="AA80" s="4" t="n">
+        <v>-1.5656</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>1.4312</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="AD80" s="4" t="n">
+        <v>-2.9059</v>
+      </c>
+      <c r="AE80" s="4" t="n">
+        <v>-2.8817</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>-2.4101</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-2.3642</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2.2569</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>-0.5517</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>-2.0647</v>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>-2.0389</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>1.0379</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>-2.7146</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>-2.4623</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>-2.7015</v>
+      </c>
+      <c r="S81" s="4" t="n">
+        <v>-2.5442</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>1.6183</v>
+      </c>
+      <c r="U81" s="4" t="n">
+        <v>-2.0861</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>-1.1216</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>4.3819</v>
+      </c>
+      <c r="X81" s="4" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>4.2718</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>1.9213</v>
+      </c>
+      <c r="AA81" s="4" t="n">
+        <v>-1.7273</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="AD81" s="4" t="n">
+        <v>-2.9556</v>
+      </c>
+      <c r="AE81" s="4" t="n">
+        <v>-2.5742</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>-1.2769</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.9207</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>-0.4438</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>-1.7085</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>-1.6505</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>-3.7621</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>-3.6988</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.2297</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>-3.5366</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>-2.9844</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="U82" s="4" t="n">
+        <v>-2.8608</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>-2.0378</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>4.0346</v>
+      </c>
+      <c r="X82" s="4" t="n">
+        <v>-1.1268</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>3.9264</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="AA82" s="4" t="n">
+        <v>-2.0296</v>
+      </c>
+      <c r="AB82" s="4" t="n">
+        <v>-1.5878</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AD82" s="4" t="n">
+        <v>-2.5093</v>
+      </c>
+      <c r="AE82" s="4" t="n">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>-1.7612</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>-1.6866</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>-0.3913</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>3.5401</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>3.5362</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>-1.2502</v>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>-1.1974</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>-3.8559</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>-3.8127</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>-3.8059</v>
+      </c>
+      <c r="S83" s="4" t="n">
+        <v>-3.6884</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="U83" s="4" t="n">
+        <v>-3.017</v>
+      </c>
+      <c r="V83" s="4" t="n">
+        <v>-2.0189</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>3.5236</v>
+      </c>
+      <c r="X83" s="4" t="n">
+        <v>-1.4236</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>3.2954</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>0.8035</v>
+      </c>
+      <c r="AA83" s="4" t="n">
+        <v>-1.4988</v>
+      </c>
+      <c r="AB83" s="4" t="n">
+        <v>-1.0571</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="AD83" s="4" t="n">
+        <v>-2.7813</v>
+      </c>
+      <c r="AE83" s="4" t="n">
+        <v>-2.7605</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>-0.9604</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>-0.9393</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1.8382</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>-0.3019</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>1.7411</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2.8293</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>-0.2311</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>2.7936</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>-1.7219</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>-3.6083</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>-3.4942</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>1.0596</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>-3.4815</v>
+      </c>
+      <c r="S84" s="4" t="n">
+        <v>-3.3342</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.0325</v>
+      </c>
+      <c r="U84" s="4" t="n">
+        <v>-3.4029</v>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>-2.9042</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="X84" s="4" t="n">
+        <v>-1.3787</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>3.1946</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="AA84" s="4" t="n">
+        <v>-1.4281</v>
+      </c>
+      <c r="AB84" s="4" t="n">
+        <v>-0.7934</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AD84" s="4" t="n">
+        <v>-2.3866</v>
+      </c>
+      <c r="AE84" s="4" t="n">
+        <v>-2.3679</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(B2:B76)</f>
+      <c r="B85" s="7">
+        <f>SUM(B2:B84)</f>
         <v/>
       </c>
-      <c r="C77" s="7">
-        <f>SUM(C2:C76)</f>
+      <c r="C85" s="7">
+        <f>SUM(C2:C84)</f>
         <v/>
       </c>
-      <c r="D77" s="7">
-        <f>SUM(D2:D76)</f>
+      <c r="D85" s="7">
+        <f>SUM(D2:D84)</f>
         <v/>
       </c>
-      <c r="E77" s="7">
-        <f>SUM(E2:E76)</f>
+      <c r="E85" s="7">
+        <f>SUM(E2:E84)</f>
         <v/>
       </c>
-      <c r="F77" s="7">
-        <f>SUM(F2:F76)</f>
+      <c r="F85" s="7">
+        <f>SUM(F2:F84)</f>
         <v/>
       </c>
-      <c r="G77" s="7">
-        <f>SUM(G2:G76)</f>
+      <c r="G85" s="7">
+        <f>SUM(G2:G84)</f>
         <v/>
       </c>
-      <c r="H77" s="7">
-        <f>SUM(H2:H76)</f>
+      <c r="H85" s="7">
+        <f>SUM(H2:H84)</f>
         <v/>
       </c>
-      <c r="I77" s="7">
-        <f>SUM(I2:I76)</f>
+      <c r="I85" s="7">
+        <f>SUM(I2:I84)</f>
         <v/>
       </c>
-      <c r="J77" s="7">
-        <f>SUM(J2:J76)</f>
+      <c r="J85" s="7">
+        <f>SUM(J2:J84)</f>
         <v/>
       </c>
-      <c r="K77" s="7">
-        <f>SUM(K2:K76)</f>
+      <c r="K85" s="7">
+        <f>SUM(K2:K84)</f>
         <v/>
       </c>
-      <c r="L77" s="7">
-        <f>SUM(L2:L76)</f>
+      <c r="L85" s="7">
+        <f>SUM(L2:L84)</f>
         <v/>
       </c>
-      <c r="M77" s="7">
-        <f>SUM(M2:M76)</f>
+      <c r="M85" s="7">
+        <f>SUM(M2:M84)</f>
         <v/>
       </c>
-      <c r="N77" s="7">
-        <f>SUM(N2:N76)</f>
+      <c r="N85" s="7">
+        <f>SUM(N2:N84)</f>
         <v/>
       </c>
-      <c r="O77" s="7">
-        <f>SUM(O2:O76)</f>
+      <c r="O85" s="7">
+        <f>SUM(O2:O84)</f>
         <v/>
       </c>
-      <c r="P77" s="7">
-        <f>SUM(P2:P76)</f>
+      <c r="P85" s="7">
+        <f>SUM(P2:P84)</f>
         <v/>
       </c>
-      <c r="Q77" s="7">
-        <f>SUM(Q2:Q76)</f>
+      <c r="Q85" s="7">
+        <f>SUM(Q2:Q84)</f>
         <v/>
       </c>
-      <c r="R77" s="7">
-        <f>SUM(R2:R76)</f>
+      <c r="R85" s="7">
+        <f>SUM(R2:R84)</f>
         <v/>
       </c>
-      <c r="S77" s="7">
-        <f>SUM(S2:S76)</f>
+      <c r="S85" s="7">
+        <f>SUM(S2:S84)</f>
         <v/>
       </c>
-      <c r="T77" s="7">
-        <f>SUM(T2:T76)</f>
+      <c r="T85" s="7">
+        <f>SUM(T2:T84)</f>
         <v/>
       </c>
-      <c r="U77" s="7">
-        <f>SUM(U2:U76)</f>
+      <c r="U85" s="7">
+        <f>SUM(U2:U84)</f>
         <v/>
       </c>
-      <c r="V77" s="7">
-        <f>SUM(V2:V76)</f>
+      <c r="V85" s="7">
+        <f>SUM(V2:V84)</f>
         <v/>
       </c>
-      <c r="W77" s="7">
-        <f>SUM(W2:W76)</f>
+      <c r="W85" s="7">
+        <f>SUM(W2:W84)</f>
         <v/>
       </c>
-      <c r="X77" s="7">
-        <f>SUM(X2:X76)</f>
+      <c r="X85" s="7">
+        <f>SUM(X2:X84)</f>
         <v/>
       </c>
-      <c r="Y77" s="7">
-        <f>SUM(Y2:Y76)</f>
+      <c r="Y85" s="7">
+        <f>SUM(Y2:Y84)</f>
         <v/>
       </c>
-      <c r="Z77" s="7">
-        <f>SUM(Z2:Z76)</f>
+      <c r="Z85" s="7">
+        <f>SUM(Z2:Z84)</f>
         <v/>
       </c>
-      <c r="AA77" s="7">
-        <f>SUM(AA2:AA76)</f>
+      <c r="AA85" s="7">
+        <f>SUM(AA2:AA84)</f>
         <v/>
       </c>
-      <c r="AB77" s="7">
-        <f>SUM(AB2:AB76)</f>
+      <c r="AB85" s="7">
+        <f>SUM(AB2:AB84)</f>
         <v/>
       </c>
-      <c r="AC77" s="7">
-        <f>SUM(AC2:AC76)</f>
+      <c r="AC85" s="7">
+        <f>SUM(AC2:AC84)</f>
         <v/>
       </c>
-      <c r="AD77" s="7">
-        <f>SUM(AD2:AD76)</f>
+      <c r="AD85" s="7">
+        <f>SUM(AD2:AD84)</f>
         <v/>
       </c>
-      <c r="AE77" s="7">
-        <f>SUM(AE2:AE76)</f>
+      <c r="AE85" s="7">
+        <f>SUM(AE2:AE84)</f>
         <v/>
       </c>
     </row>
